--- a/marketing_forms/013_link_tracking_request_form--marketing_forms.xlsx
+++ b/marketing_forms/013_link_tracking_request_form--marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1129,8 +1129,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'text'}</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'text'}</t>
+          <t>text</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'image'}</t>
+          <t>image</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'image'}</t>
+          <t>image</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'email'}</t>
+          <t>email</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'communications'}</t>
+          <t>communications</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'communications'}</t>
+          <t>communications</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'analytics'}</t>
+          <t>analytics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'analytics'}</t>
+          <t>analytics</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'others'}</t>
+          <t>others</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'others'}</t>
+          <t>others</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'once'}</t>
+          <t>once</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'once'}</t>
+          <t>once</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'read'}</t>
+          <t>read</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'read'}</t>
+          <t>read</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'edit'}</t>
+          <t>edit</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'edit'}</t>
+          <t>edit</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
